--- a/Output Data Tables/AFAT Outputs/Aggregated Tables/2025/Airline_Cumulative_Financial_Statistics_2025.xlsx
+++ b/Output Data Tables/AFAT Outputs/Aggregated Tables/2025/Airline_Cumulative_Financial_Statistics_2025.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="40" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="44" uniqueCount="44">
   <si>
     <t>Row</t>
   </si>
@@ -85,6 +85,18 @@
   </si>
   <si>
     <t>SkyWest</t>
+  </si>
+  <si>
+    <t>FSC</t>
+  </si>
+  <si>
+    <t>Hybrid</t>
+  </si>
+  <si>
+    <t>ULCC</t>
+  </si>
+  <si>
+    <t>Regional</t>
   </si>
   <si>
     <t>All Airlines</t>
@@ -178,7 +190,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:P25"/>
+  <dimension ref="A1:P29"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.42578125" customWidth="true"/>
@@ -204,49 +216,49 @@
         <v>0</v>
       </c>
       <c r="B1" s="0" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="C1" s="0" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="D1" s="0" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="E1" s="0" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="F1" s="0" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="G1" s="0" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="H1" s="0" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="I1" s="0" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="J1" s="0" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="K1" s="0" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="L1" s="0" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="M1" s="0" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="N1" s="0" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="O1" s="0" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="P1" s="0" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
     </row>
     <row r="2">
@@ -1404,48 +1416,248 @@
         <v>24</v>
       </c>
       <c r="B25" s="0">
+        <v>142748025850</v>
+      </c>
+      <c r="C25" s="0">
+        <v>0.16739999999999999</v>
+      </c>
+      <c r="D25" s="0">
+        <v>244.55000000000001</v>
+      </c>
+      <c r="E25" s="0">
+        <v>0.20080000000000001</v>
+      </c>
+      <c r="F25" s="0">
+        <v>297.69999999999999</v>
+      </c>
+      <c r="G25" s="0">
+        <v>145162797160</v>
+      </c>
+      <c r="H25" s="0">
+        <v>0.17030000000000001</v>
+      </c>
+      <c r="I25" s="0">
+        <v>248.69</v>
+      </c>
+      <c r="J25" s="0">
+        <v>0.20419999999999999</v>
+      </c>
+      <c r="K25" s="0">
+        <v>302.73000000000002</v>
+      </c>
+      <c r="L25" s="0">
+        <v>308233</v>
+      </c>
+      <c r="M25" s="0">
+        <v>2766078</v>
+      </c>
+      <c r="N25" s="0">
+        <v>187150</v>
+      </c>
+      <c r="O25" s="0">
+        <v>470952</v>
+      </c>
+      <c r="P25" s="0">
+        <v>14.779999999999999</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="0" t="s">
+        <v>25</v>
+      </c>
+      <c r="B26" s="0">
+        <v>50007385280</v>
+      </c>
+      <c r="C26" s="0">
+        <v>0.1477</v>
+      </c>
+      <c r="D26" s="0">
+        <v>145.06</v>
+      </c>
+      <c r="E26" s="0">
+        <v>0.185</v>
+      </c>
+      <c r="F26" s="0">
+        <v>190.05000000000001</v>
+      </c>
+      <c r="G26" s="0">
+        <v>48410300200</v>
+      </c>
+      <c r="H26" s="0">
+        <v>0.14299999999999999</v>
+      </c>
+      <c r="I26" s="0">
+        <v>140.43000000000001</v>
+      </c>
+      <c r="J26" s="0">
+        <v>0.17910000000000001</v>
+      </c>
+      <c r="K26" s="0">
+        <v>183.97999999999999</v>
+      </c>
+      <c r="L26" s="0">
+        <v>120137</v>
+      </c>
+      <c r="M26" s="0">
+        <v>2818830</v>
+      </c>
+      <c r="N26" s="0">
+        <v>186737</v>
+      </c>
+      <c r="O26" s="0">
+        <v>402959</v>
+      </c>
+      <c r="P26" s="0">
+        <v>15.1</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="0" t="s">
+        <v>26</v>
+      </c>
+      <c r="B27" s="0">
+        <v>12238631360</v>
+      </c>
+      <c r="C27" s="0">
+        <v>0.10979999999999999</v>
+      </c>
+      <c r="D27" s="0">
+        <v>103.44</v>
+      </c>
+      <c r="E27" s="0">
+        <v>0.13900000000000001</v>
+      </c>
+      <c r="F27" s="0">
+        <v>133.41</v>
+      </c>
+      <c r="G27" s="0">
+        <v>11124110450</v>
+      </c>
+      <c r="H27" s="0">
+        <v>0.0998</v>
+      </c>
+      <c r="I27" s="0">
+        <v>94.019999999999996</v>
+      </c>
+      <c r="J27" s="0">
+        <v>0.12640000000000001</v>
+      </c>
+      <c r="K27" s="0">
+        <v>121.26000000000001</v>
+      </c>
+      <c r="L27" s="0">
+        <v>27266</v>
+      </c>
+      <c r="M27" s="0">
+        <v>4087437</v>
+      </c>
+      <c r="N27" s="0">
+        <v>144740</v>
+      </c>
+      <c r="O27" s="0">
+        <v>407985</v>
+      </c>
+      <c r="P27" s="0">
+        <v>28.239999999999998</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="0" t="s">
+        <v>27</v>
+      </c>
+      <c r="B28" s="0">
+        <v>11586376460</v>
+      </c>
+      <c r="C28" s="0">
+        <v>0.14019999999999999</v>
+      </c>
+      <c r="D28" s="0">
+        <v>66.090000000000003</v>
+      </c>
+      <c r="E28" s="0">
+        <v>0.17460000000000001</v>
+      </c>
+      <c r="F28" s="0">
+        <v>83.099999999999994</v>
+      </c>
+      <c r="G28" s="0">
+        <v>11367738000</v>
+      </c>
+      <c r="H28" s="0">
+        <v>0.1376</v>
+      </c>
+      <c r="I28" s="0">
+        <v>64.849999999999994</v>
+      </c>
+      <c r="J28" s="0">
+        <v>0.17130000000000001</v>
+      </c>
+      <c r="K28" s="0">
+        <v>81.530000000000001</v>
+      </c>
+      <c r="L28" s="0">
+        <v>65492</v>
+      </c>
+      <c r="M28" s="0">
+        <v>1261537</v>
+      </c>
+      <c r="N28" s="0">
+        <v>107923</v>
+      </c>
+      <c r="O28" s="0">
+        <v>173574</v>
+      </c>
+      <c r="P28" s="0">
+        <v>11.69</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="0" t="s">
+        <v>28</v>
+      </c>
+      <c r="B29" s="0">
         <v>216580418950</v>
       </c>
-      <c r="C25" s="0">
+      <c r="C29" s="0">
         <v>0.15629999999999999</v>
       </c>
-      <c r="D25" s="0">
+      <c r="D29" s="0">
         <v>177.22</v>
       </c>
-      <c r="E25" s="0">
+      <c r="E29" s="0">
         <v>0.1908</v>
       </c>
-      <c r="F25" s="0">
+      <c r="F29" s="0">
         <v>222.41</v>
       </c>
-      <c r="G25" s="0">
+      <c r="G29" s="0">
         <v>216064945810</v>
       </c>
-      <c r="H25" s="0">
+      <c r="H29" s="0">
         <v>0.156</v>
       </c>
-      <c r="I25" s="0">
+      <c r="I29" s="0">
         <v>176.80000000000001</v>
       </c>
-      <c r="J25" s="0">
+      <c r="J29" s="0">
         <v>0.1903</v>
       </c>
-      <c r="K25" s="0">
+      <c r="K29" s="0">
         <v>221.88</v>
       </c>
-      <c r="L25" s="0">
+      <c r="L29" s="0">
         <v>521128</v>
       </c>
-      <c r="M25" s="0">
+      <c r="M29" s="0">
         <v>2658293</v>
       </c>
-      <c r="N25" s="0">
+      <c r="N29" s="0">
         <v>174879</v>
       </c>
-      <c r="O25" s="0">
+      <c r="O29" s="0">
         <v>414610</v>
       </c>
-      <c r="P25" s="0">
+      <c r="P29" s="0">
         <v>15.199999999999999</v>
       </c>
     </row>
